--- a/owners1.xlsx
+++ b/owners1.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f25347fadc9be86b/Documents/MaintApp/MaintApp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{478ADE98-C619-4020-A932-D31BD5BA4D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B39B1FBA-5CEE-4AC3-AB09-9579F5CAE369}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{478ADE98-C619-4020-A932-D31BD5BA4D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6C8CF52-04BF-4385-A251-D47FEB7FD843}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Details MC " sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Details MC '!$A$1:$E$70</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Details MC '!$A$1:$E$66</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="119">
   <si>
     <t>Dr. Narendranath Pal</t>
   </si>
@@ -105,15 +105,9 @@
     <t>Dr. Rajkumar Sangiri</t>
   </si>
   <si>
-    <t>1F+1H</t>
-  </si>
-  <si>
     <t>1G</t>
   </si>
   <si>
-    <t>2A+2C</t>
-  </si>
-  <si>
     <t>Rahul Kundu</t>
   </si>
   <si>
@@ -253,9 +247,6 @@
   </si>
   <si>
     <t>Anita Lo Saha</t>
-  </si>
-  <si>
-    <t>5E+5G</t>
   </si>
   <si>
     <t>Sangita Roy</t>
@@ -386,12 +377,6 @@
     </r>
   </si>
   <si>
-    <t>Mintu Sk</t>
-  </si>
-  <si>
-    <t>Omprakash</t>
-  </si>
-  <si>
     <t>Deb Kumar Mondal</t>
   </si>
   <si>
@@ -404,13 +389,16 @@
     <t>Soumen Patra</t>
   </si>
   <si>
-    <t>Shanti Da Grill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abhishek </t>
-  </si>
-  <si>
     <t>empty</t>
+  </si>
+  <si>
+    <t>1F+H</t>
+  </si>
+  <si>
+    <t>2A+C</t>
+  </si>
+  <si>
+    <t>5E+G</t>
   </si>
 </sst>
 </file>
@@ -495,7 +483,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -544,15 +532,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -564,46 +543,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -673,35 +617,20 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -718,10 +647,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1014,43 +939,43 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E66"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.109375" customWidth="1"/>
+    <col min="1" max="1" width="14.1640625" customWidth="1"/>
     <col min="2" max="2" width="49.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" customWidth="1"/>
+    <col min="3" max="3" width="16.1640625" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="22.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.5" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-    </row>
-    <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-    </row>
-    <row r="3" spans="1:5" ht="65.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:5" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="31"/>
-    </row>
-    <row r="5" spans="1:5" s="2" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+    </row>
+    <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="24"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+    </row>
+    <row r="3" spans="1:5" ht="65.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:5" ht="44.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="27"/>
+    </row>
+    <row r="5" spans="1:5" s="2" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
         <v>4</v>
       </c>
@@ -1067,7 +992,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>1</v>
       </c>
@@ -1084,7 +1009,7 @@
         <v>9609688683</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>2</v>
       </c>
@@ -1101,7 +1026,7 @@
         <v>7557076444</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>3</v>
       </c>
@@ -1118,7 +1043,7 @@
         <v>8001604274</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>4</v>
       </c>
@@ -1133,7 +1058,7 @@
       </c>
       <c r="E9" s="10"/>
     </row>
-    <row r="10" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>5</v>
       </c>
@@ -1150,7 +1075,7 @@
         <v>9434115212</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>6</v>
       </c>
@@ -1158,7 +1083,7 @@
         <v>22</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>23</v>
+        <v>116</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>11</v>
@@ -1167,7 +1092,7 @@
         <v>9474561244</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>7</v>
       </c>
@@ -1175,7 +1100,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12" s="7">
         <v>2</v>
@@ -1184,7 +1109,7 @@
         <v>9475044158</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>8</v>
       </c>
@@ -1192,7 +1117,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>25</v>
+        <v>117</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>11</v>
@@ -1201,15 +1126,15 @@
         <v>9933111420</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>9</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D14" s="7">
         <v>3</v>
@@ -1218,26 +1143,26 @@
         <v>9427221065</v>
       </c>
     </row>
-    <row r="15" spans="1:5" s="19" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" s="19" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="14">
         <v>10</v>
       </c>
       <c r="B15" s="15"/>
       <c r="C15" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D15" s="17"/>
       <c r="E15" s="18"/>
     </row>
-    <row r="16" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>11</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D16" s="7">
         <v>3</v>
@@ -1246,15 +1171,15 @@
         <v>8962744280</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>12</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D17" s="7">
         <v>3</v>
@@ -1263,15 +1188,15 @@
         <v>9749543529</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>13</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D18" s="7">
         <v>2</v>
@@ -1280,28 +1205,28 @@
         <v>7001420328</v>
       </c>
     </row>
-    <row r="19" spans="1:5" s="19" customFormat="1" ht="22.8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" s="19" customFormat="1" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A19" s="14">
         <v>14</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D19" s="17"/>
       <c r="E19" s="18"/>
     </row>
-    <row r="20" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>15</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D20" s="7">
         <v>3</v>
@@ -1310,15 +1235,15 @@
         <v>8918008545</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>16</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D21" s="7">
         <v>3</v>
@@ -1327,15 +1252,15 @@
         <v>8967856644</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>17</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D22" s="7">
         <v>2</v>
@@ -1344,37 +1269,37 @@
         <v>8436193278</v>
       </c>
     </row>
-    <row r="23" spans="1:5" s="19" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" s="19" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="14">
         <v>18</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D23" s="17"/>
       <c r="E23" s="18"/>
     </row>
-    <row r="24" spans="1:5" s="19" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" s="19" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="14">
         <v>19</v>
       </c>
       <c r="B24" s="15"/>
       <c r="C24" s="16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D24" s="17"/>
       <c r="E24" s="18"/>
     </row>
-    <row r="25" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>20</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D25" s="7">
         <v>3</v>
@@ -1383,15 +1308,15 @@
         <v>9474039781</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>21</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D26" s="7">
         <v>2</v>
@@ -1400,15 +1325,15 @@
         <v>8789747535</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>22</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D27" s="7">
         <v>2</v>
@@ -1417,15 +1342,15 @@
         <v>9732006006</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>23</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D28" s="7">
         <v>3</v>
@@ -1434,32 +1359,32 @@
         <v>8927777001</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>24</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D29" s="7">
         <v>3</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>25</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D30" s="7">
         <v>2</v>
@@ -1468,26 +1393,26 @@
         <v>9775033283</v>
       </c>
     </row>
-    <row r="31" spans="1:5" s="19" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" s="19" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="14">
         <v>26</v>
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D31" s="17"/>
       <c r="E31" s="18"/>
     </row>
-    <row r="32" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>27</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D32" s="7">
         <v>3</v>
@@ -1496,15 +1421,15 @@
         <v>9007993440</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>28</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D33" s="7">
         <v>3</v>
@@ -1513,15 +1438,15 @@
         <v>9851121248</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>29</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D34" s="7">
         <v>2</v>
@@ -1530,15 +1455,15 @@
         <v>7908578532</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>30</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D35" s="7">
         <v>2</v>
@@ -1547,15 +1472,15 @@
         <v>8637853169</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>31</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D36" s="7">
         <v>3</v>
@@ -1564,15 +1489,15 @@
         <v>9434101485</v>
       </c>
     </row>
-    <row r="37" spans="1:5" s="19" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" s="19" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="14">
         <v>32</v>
       </c>
-      <c r="B37" s="28" t="s">
-        <v>119</v>
+      <c r="B37" s="23" t="s">
+        <v>114</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D37" s="17">
         <v>3</v>
@@ -1581,15 +1506,15 @@
         <v>8820411025</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>33</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D38" s="7">
         <v>2</v>
@@ -1598,15 +1523,15 @@
         <v>9749449845</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>34</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D39" s="7">
         <v>2</v>
@@ -1615,15 +1540,15 @@
         <v>9735135784</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>35</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>12</v>
@@ -1632,15 +1557,15 @@
         <v>9474567580</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>36</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D41" s="7">
         <v>3</v>
@@ -1649,15 +1574,15 @@
         <v>9836087162</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>37</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D42" s="7">
         <v>2</v>
@@ -1666,15 +1591,15 @@
         <v>8101850717</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>38</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D43" s="7">
         <v>3</v>
@@ -1683,15 +1608,15 @@
         <v>8318151358</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>39</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D44" s="7">
         <v>3</v>
@@ -1700,15 +1625,15 @@
         <v>6296936814</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>40</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D45" s="7">
         <v>2</v>
@@ -1717,26 +1642,26 @@
         <v>9531571901</v>
       </c>
     </row>
-    <row r="46" spans="1:5" s="19" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" s="19" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="14">
         <v>41</v>
       </c>
       <c r="B46" s="15"/>
       <c r="C46" s="16" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D46" s="17"/>
       <c r="E46" s="18"/>
     </row>
-    <row r="47" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
         <v>42</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D47" s="7">
         <v>3</v>
@@ -1745,58 +1670,58 @@
         <v>7680914260</v>
       </c>
     </row>
-    <row r="48" spans="1:5" s="19" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" s="19" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="14">
         <v>43</v>
       </c>
-      <c r="B48" s="28" t="s">
-        <v>116</v>
+      <c r="B48" s="23" t="s">
+        <v>111</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D48" s="17"/>
       <c r="E48" s="18">
         <v>7044376634</v>
       </c>
     </row>
-    <row r="49" spans="1:5" s="19" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" s="19" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="14">
         <v>44</v>
       </c>
-      <c r="B49" s="28" t="s">
-        <v>117</v>
+      <c r="B49" s="23" t="s">
+        <v>112</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D49" s="17"/>
       <c r="E49" s="18">
         <v>7908550094</v>
       </c>
     </row>
-    <row r="50" spans="1:5" s="19" customFormat="1" ht="22.8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" s="19" customFormat="1" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A50" s="14">
         <v>45</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D50" s="17"/>
       <c r="E50" s="18"/>
     </row>
-    <row r="51" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <v>46</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D51" s="7">
         <v>3</v>
@@ -1805,15 +1730,15 @@
         <v>7908182143</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>47</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D52" s="7">
         <v>3</v>
@@ -1822,41 +1747,41 @@
         <v>9933918646</v>
       </c>
     </row>
-    <row r="53" spans="1:5" s="19" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" s="19" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="14">
         <v>48</v>
       </c>
-      <c r="B53" s="28" t="s">
-        <v>118</v>
+      <c r="B53" s="23" t="s">
+        <v>113</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D53" s="17"/>
       <c r="E53" s="18">
         <v>9831313288</v>
       </c>
     </row>
-    <row r="54" spans="1:5" s="19" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" s="19" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="14">
         <v>49</v>
       </c>
       <c r="B54" s="15"/>
       <c r="C54" s="16" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D54" s="17"/>
       <c r="E54" s="18"/>
     </row>
-    <row r="55" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>50</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D55" s="7">
         <v>3</v>
@@ -1865,15 +1790,15 @@
         <v>9681710268</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
         <v>51</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D56" s="7">
         <v>3</v>
@@ -1882,15 +1807,15 @@
         <v>9434216284</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
         <v>52</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D57" s="7">
         <v>2</v>
@@ -1899,80 +1824,80 @@
         <v>9458208175</v>
       </c>
     </row>
-    <row r="58" spans="1:5" s="19" customFormat="1" ht="22.8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" s="19" customFormat="1" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A58" s="14">
         <v>53</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D58" s="17"/>
       <c r="E58" s="18"/>
     </row>
-    <row r="59" spans="1:5" s="19" customFormat="1" ht="22.8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" s="19" customFormat="1" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A59" s="14">
         <v>54</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D59" s="17"/>
       <c r="E59" s="18"/>
     </row>
-    <row r="60" spans="1:5" s="19" customFormat="1" ht="22.8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" s="19" customFormat="1" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A60" s="14">
         <v>55</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D60" s="17"/>
       <c r="E60" s="18"/>
     </row>
-    <row r="61" spans="1:5" s="19" customFormat="1" ht="22.8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" s="19" customFormat="1" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A61" s="14">
         <v>56</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D61" s="17"/>
       <c r="E61" s="18"/>
     </row>
-    <row r="62" spans="1:5" s="19" customFormat="1" ht="22.8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" s="19" customFormat="1" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A62" s="14">
         <v>57</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D62" s="17"/>
       <c r="E62" s="18"/>
     </row>
-    <row r="63" spans="1:5" ht="22.8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
         <v>58</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D63" s="7">
         <v>3</v>
@@ -1981,15 +1906,15 @@
         <v>9681429435</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
         <v>59</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D64" s="7">
         <v>3</v>
@@ -1998,15 +1923,15 @@
         <v>7908970236</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
         <v>60</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D65" s="7">
         <v>2</v>
@@ -2015,7 +1940,7 @@
         <v>9046420491</v>
       </c>
     </row>
-    <row r="66" spans="1:5" s="19" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" s="19" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="14">
         <v>61</v>
       </c>
@@ -2025,50 +1950,6 @@
       </c>
       <c r="D66" s="17"/>
       <c r="E66" s="21"/>
-    </row>
-    <row r="67" spans="1:5" s="19" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="23">
-        <v>62</v>
-      </c>
-      <c r="B67" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="C67" s="25"/>
-      <c r="D67" s="26"/>
-      <c r="E67" s="27"/>
-    </row>
-    <row r="68" spans="1:5" s="19" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="14">
-        <v>63</v>
-      </c>
-      <c r="B68" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="C68" s="25"/>
-      <c r="D68" s="26"/>
-      <c r="E68" s="27"/>
-    </row>
-    <row r="69" spans="1:5" s="19" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="23">
-        <v>64</v>
-      </c>
-      <c r="B69" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="C69" s="25"/>
-      <c r="D69" s="26"/>
-      <c r="E69" s="27"/>
-    </row>
-    <row r="70" spans="1:5" s="19" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="23">
-        <v>65</v>
-      </c>
-      <c r="B70" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="C70" s="25"/>
-      <c r="D70" s="26"/>
-      <c r="E70" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2077,6 +1958,6 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="44" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="45" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>